--- a/Saved_Lists/Inventory.xlsx
+++ b/Saved_Lists/Inventory.xlsx
@@ -757,7 +757,7 @@
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="7">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
@@ -773,9 +773,6 @@
     </xf>
     <xf borderId="0" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment horizontal="right" vertical="bottom"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment horizontal="right" readingOrder="0" vertical="bottom"/>
@@ -3476,8 +3473,8 @@
       <c r="E8" s="2" t="s">
         <v>215</v>
       </c>
-      <c r="F8" s="6">
-        <v>2.0</v>
+      <c r="F8" s="2">
+        <v>1.0</v>
       </c>
     </row>
     <row r="9">
@@ -3493,11 +3490,11 @@
       <c r="D9" s="3" t="s">
         <v>219</v>
       </c>
-      <c r="E9" s="7">
+      <c r="E9" s="6">
         <v>25.27</v>
       </c>
-      <c r="F9" s="7">
-        <v>3.0</v>
+      <c r="F9" s="6">
+        <v>1.0</v>
       </c>
     </row>
     <row r="21" ht="15.75" customHeight="1"/>

--- a/Saved_Lists/Inventory.xlsx
+++ b/Saved_Lists/Inventory.xlsx
@@ -1158,7 +1158,7 @@
         <v>25.27</v>
       </c>
       <c r="F9" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
     </row>
   </sheetData>

--- a/Saved_Lists/Inventory.xlsx
+++ b/Saved_Lists/Inventory.xlsx
@@ -436,7 +436,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F1"/>
+  <dimension ref="A1:F9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -469,6 +469,198 @@
         <is>
           <t>Quantity</t>
         </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>311-9.76KCRCT-ND</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>RC0805FR-079K76L</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>RES 9.76K OHM 1% 1/8W 0805</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr"/>
+      <c r="E2" t="n">
+        <v>0.062</v>
+      </c>
+      <c r="F2" t="n">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>541-4138-1-ND</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>CRCW08054K99FKEAC</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>RES SMD 4.99K OHM 1% 1/8W 0805</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr"/>
+      <c r="E3" t="n">
+        <v>0.092</v>
+      </c>
+      <c r="F3" t="n">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>311-1.00CRCT-ND</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>RC0805FR-071RL</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>RES 1 OHM 1% 1/8W 0805</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr"/>
+      <c r="E4" t="n">
+        <v>0.122</v>
+      </c>
+      <c r="F4" t="n">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>311-1.00KCRCT-ND</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>RC0805FR-071KL</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>RES 1K OHM 1% 1/8W 0805</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr"/>
+      <c r="E5" t="n">
+        <v>0.062</v>
+      </c>
+      <c r="F5" t="n">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>RNCP0805FTD10K0CT-ND</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>RNCP0805FTD10K0</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>RES 10K OHM 1% 1/4W 0805</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr"/>
+      <c r="E6" t="n">
+        <v>0.0439</v>
+      </c>
+      <c r="F6" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>2019-RK73H2ATTD2200FCT-ND</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>RK73H2ATTD2200F</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>RES 220 OHM 1% 1/4W 0805</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr"/>
+      <c r="E7" t="n">
+        <v>0.0253</v>
+      </c>
+      <c r="F7" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>HS505RF-ND</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>HS50 5R F</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>RES CHAS MNT 5 OHM 1% 50W</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr"/>
+      <c r="E8" t="n">
+        <v>5.86</v>
+      </c>
+      <c r="F8" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>311-1.47KCRCT-ND</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>RC0805FR-071K47L</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>RES 1.47K OHM 1% 1/8W 0805</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr"/>
+      <c r="E9" t="n">
+        <v>0.0208</v>
+      </c>
+      <c r="F9" t="n">
+        <v>100</v>
       </c>
     </row>
   </sheetData>
@@ -482,7 +674,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F1"/>
+  <dimension ref="A1:F7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -515,6 +707,150 @@
         <is>
           <t>Quantity</t>
         </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>732-4982-1-ND</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>150080BS75000</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>LED BLUE CLEAR 0805 SMD</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr"/>
+      <c r="E2" t="n">
+        <v>0.27</v>
+      </c>
+      <c r="F2" t="n">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>732-4986-1-ND</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>150080VS75000</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>LED GREEN CLEAR 0805 SMD</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr"/>
+      <c r="E3" t="n">
+        <v>0.27</v>
+      </c>
+      <c r="F3" t="n">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>732-4985-1-ND</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>150080SS75000</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>LED RED CLEAR 0805 SMD</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr"/>
+      <c r="E4" t="n">
+        <v>0.27</v>
+      </c>
+      <c r="F4" t="n">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>1125-1191-ND</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>MT5470D-UY</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>LED YELLOW DIFFUSED 5MM OVAL T/H</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr"/>
+      <c r="E5" t="n">
+        <v>0.77</v>
+      </c>
+      <c r="F5" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>C5SMF-RJE-CU14QBB2CT-ND</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>C5SMF-RJE-CU14QBB2</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>LED RED CLEAR 5MM OVAL T/H</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr"/>
+      <c r="E6" t="n">
+        <v>0.29</v>
+      </c>
+      <c r="F6" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>C5SMF-GJE-CX14Q7T2CT-ND</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>C5SMF-GJE-CX14Q7T2</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>LED GREEN CLEAR 5MM OVAL T/H</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr"/>
+      <c r="E7" t="n">
+        <v>0.46</v>
+      </c>
+      <c r="F7" t="n">
+        <v>5</v>
       </c>
     </row>
   </sheetData>
@@ -528,7 +864,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F1"/>
+  <dimension ref="A1:F2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -561,6 +897,30 @@
         <is>
           <t>Quantity</t>
         </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>1738-1038-ND</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>DFR0229</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>MICROSD CARD MODULE FOR ARDUINO</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr"/>
+      <c r="E2" t="n">
+        <v>7.16</v>
+      </c>
+      <c r="F2" t="n">
+        <v>1</v>
       </c>
     </row>
   </sheetData>
@@ -574,7 +934,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F1"/>
+  <dimension ref="A1:F10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -607,6 +967,222 @@
         <is>
           <t>Quantity</t>
         </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>PCB-RULER-ND</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>DKS-PCB-RULER-12INCH</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>PCB LAYOUT REFERENCE RULER 12"</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr"/>
+      <c r="E2" t="n">
+        <v>7.26</v>
+      </c>
+      <c r="F2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>1738-1041-ND</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>DFR0299</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>DFPLAYER - A MINI MP3 PLAYER</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr"/>
+      <c r="E3" t="n">
+        <v>8.19</v>
+      </c>
+      <c r="F3" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>433-1259-ND</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>SP-3005Y</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>SPEAKER 8OHM 1W TOP PORT 87DB</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr"/>
+      <c r="E4" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="F4" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>1570-MR3010E12B1+6-RSR-ND</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>MR3010E12B1+6-RSR</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>FAN AXIAL 30X10MM 12VDC WIRE</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr"/>
+      <c r="E5" t="n">
+        <v>25.2</v>
+      </c>
+      <c r="F5" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>1939-1070-ND</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>GTM43007-B6030-FW(R)</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>AC/DC CONVERTER 30V 60W</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr"/>
+      <c r="E6" t="n">
+        <v>21.84</v>
+      </c>
+      <c r="F6" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>1528-1031-ND</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>1752</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>EVAL BOARD FOR MAX9744</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr"/>
+      <c r="E7" t="n">
+        <v>28.74</v>
+      </c>
+      <c r="F7" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>2056-FR10HM-4OHM-ND</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>FR 10 HM - 4 OHM</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>SPEAKER 4OHM 20W TOP PORT 86DB</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr"/>
+      <c r="E8" t="n">
+        <v>14.13</v>
+      </c>
+      <c r="F8" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>1568-1600-ND</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>COM-10001</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>KNOB KNURLED 0.236" METAL</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr"/>
+      <c r="E9" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="F9" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Q1185-ND</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>QFWB-65-12-US01</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>AC/DC WALL MOUNT ADAPTER 12V 60W</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr"/>
+      <c r="E10" t="n">
+        <v>25.27</v>
+      </c>
+      <c r="F10" t="n">
+        <v>1</v>
       </c>
     </row>
   </sheetData>
@@ -620,7 +1196,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F1"/>
+  <dimension ref="A1:F6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -653,6 +1229,134 @@
         <is>
           <t>Quantity</t>
         </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>399-C0805C103K1RAC7800CT-ND</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>C0805C103K1RAC7800</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>CAP CER 10000PF 100V X7R 0805</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>10NF OR 0.01UF</t>
+        </is>
+      </c>
+      <c r="E2" t="n">
+        <v>0.081</v>
+      </c>
+      <c r="F2" t="n">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>399-C0805C104K5RAC7800CT-ND</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>C0805C104K5RAC7800</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>CAP CER 0.1UF 50V X7R 0805</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>100NF OR 0.1UF</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>0.145</v>
+      </c>
+      <c r="F3" t="n">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>P16560CT-ND</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>35SVPF22M</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>CAP ALUM POLY 22UF 20% 35V SMD</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr"/>
+      <c r="E4" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="F4" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>399-A768MS107M1HLAE024CT-ND</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>A768MS107M1HLAE024</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>CAP ALUM POLY 100UF 20% 50V SMD</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr"/>
+      <c r="E5" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="F5" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>1276-1002-1-ND</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>CL05B104KP5NNNC</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>CAP CER 0.1UF 10V X7R 0402</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr"/>
+      <c r="E6" t="n">
+        <v>0.0154</v>
+      </c>
+      <c r="F6" t="n">
+        <v>100</v>
       </c>
     </row>
   </sheetData>
@@ -666,7 +1370,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F1"/>
+  <dimension ref="A1:F2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -699,6 +1403,30 @@
         <is>
           <t>Quantity</t>
         </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>PCD2434CT-ND</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>ETQ-P5M330YFC</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>FIXED IND 33UH 5A 75.4 MOHM SMD</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr"/>
+      <c r="E2" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="F2" t="n">
+        <v>3</v>
       </c>
     </row>
   </sheetData>
@@ -712,7 +1440,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F1"/>
+  <dimension ref="A1:F4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -745,6 +1473,78 @@
         <is>
           <t>Quantity</t>
         </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>1514-PN2222APBFREE-ND</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>PN2222A PBFREE</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>TRANS NPN 40V 0.8A TO92-3</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr"/>
+      <c r="E2" t="n">
+        <v>0.67</v>
+      </c>
+      <c r="F2" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>PZT2222AT1GOSCT-ND</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>PZT2222AT1G</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>TRANS NPN 40V 0.6A SOT223</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr"/>
+      <c r="E3" t="n">
+        <v>0.64</v>
+      </c>
+      <c r="F3" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>497-5236-1-ND</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>2STD1665T4</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>TRANS NPN 65V 6A DPAK</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr"/>
+      <c r="E4" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="F4" t="n">
+        <v>1</v>
       </c>
     </row>
   </sheetData>
@@ -758,7 +1558,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F1"/>
+  <dimension ref="A1:F5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -791,6 +1591,102 @@
         <is>
           <t>Quantity</t>
         </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>SB5100DICT-ND</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>SB5100-T</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>DIODE SCHOTTKY 100V 5A DO201AD</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr"/>
+      <c r="E2" t="n">
+        <v>0.899</v>
+      </c>
+      <c r="F2" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>SK54B-LTPMSCT-ND</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>SK54B-LTP</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>DIODE SCHOTTKY 40V 5A DO214AA</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr"/>
+      <c r="E3" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="F3" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>FDLL4148CT-ND</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>FDLL4148</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>DIODE GEN PURP 100V 200MA SOD80</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr"/>
+      <c r="E4" t="n">
+        <v>0.143</v>
+      </c>
+      <c r="F4" t="n">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>1655-DSS14UCT-ND</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>DSS14U</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>DIODE SCHOTTKY 40V 1A SOD123FL</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr"/>
+      <c r="E5" t="n">
+        <v>0.263</v>
+      </c>
+      <c r="F5" t="n">
+        <v>10</v>
       </c>
     </row>
   </sheetData>
@@ -804,7 +1700,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F2"/>
+  <dimension ref="A1:F8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -861,6 +1757,150 @@
       <c r="E2" t="inlineStr"/>
       <c r="F2" t="n">
         <v>3.97</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>5</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>296-1414-5-ND</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>RC4558P</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>IC OPAMP GP 2 CIRCUIT 8DIP</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr"/>
+      <c r="F3" t="n">
+        <v>0.63</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>5</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>296-NE555P-ND</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>NE555P</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>IC OSC SINGLE TIMER 100KHZ 8-DIP</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr"/>
+      <c r="F4" t="n">
+        <v>0.59</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>3</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>296-43515-5-ND</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>LM2679S-ADJ/NOPB</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>IC REG BUCK ADJ 5A TO263-7</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr"/>
+      <c r="F5" t="n">
+        <v>11.01</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>3</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>296-14118-5-ND</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>CD4056BE</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>IC DRVR 7 SEGMENT 1 DIGIT 16DIP</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr"/>
+      <c r="F6" t="n">
+        <v>1.02</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>3</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>296-31512-1-ND</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>CD4056BM96</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>IC DRVR 7 SEGMENT 1 DIGIT 16SOIC</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr"/>
+      <c r="F7" t="n">
+        <v>0.8</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>10</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>AS78L05RTR-G1DICT-ND</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>AS78L05RTR-G1</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>IC REG LINEAR 5V 100MA SOT89-3</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr"/>
+      <c r="F8" t="n">
+        <v>0.505</v>
       </c>
     </row>
   </sheetData>
@@ -874,7 +1914,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F1"/>
+  <dimension ref="A1:F9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -907,6 +1947,198 @@
         <is>
           <t>Quantity</t>
         </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>A98333-ND</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>282834-2</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>TERM BLK 2P SIDE ENT 2.54MM PCB</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr"/>
+      <c r="E2" t="n">
+        <v>2.01</v>
+      </c>
+      <c r="F2" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>ED10563-ND</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>OSTVN04A150</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>TERM BLK 4P SIDE ENT 2.54MM PCB</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr"/>
+      <c r="E3" t="n">
+        <v>2.01</v>
+      </c>
+      <c r="F3" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>2092-SX1100-B-ND</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>SX1100-B</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>CONN SHUNT BLACK OPEN TOP</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr"/>
+      <c r="E4" t="n">
+        <v>0.078</v>
+      </c>
+      <c r="F4" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>GC399-ND</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>33-1402</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>CONN BARRIER SPKR STRIP 2CIRCUIT</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr"/>
+      <c r="E5" t="n">
+        <v>3.54</v>
+      </c>
+      <c r="F5" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>A98077-ND</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>282836-3</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>TERM BLK 3POS SIDE ENTRY 5MM PCB</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr"/>
+      <c r="E6" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="F6" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>455-2271-ND</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>B6B-XH-A(LF)(SN)</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>CONN HEADER VERT 6POS 2.5MM</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr"/>
+      <c r="E7" t="n">
+        <v>0.367</v>
+      </c>
+      <c r="F7" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>455-2218-ND</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>XHP-6</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>CONN RCPT HSG 6POS 2.50MM</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr"/>
+      <c r="E8" t="n">
+        <v>0.182</v>
+      </c>
+      <c r="F8" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>455-2261-1-ND</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>SXH-002T-P0.6</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>CONN SOCKET 26-30AWG CRIMP TIN</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr"/>
+      <c r="E9" t="n">
+        <v>0.0546</v>
+      </c>
+      <c r="F9" t="n">
+        <v>50</v>
       </c>
     </row>
   </sheetData>
@@ -920,7 +2152,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F1"/>
+  <dimension ref="A1:F2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -953,6 +2185,30 @@
         <is>
           <t>Quantity</t>
         </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>1830-1161-ND</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>INND-TS56RCB</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>DISPLAY 7SEG 0.56" SGL RED 10DIP</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr"/>
+      <c r="E2" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="F2" t="n">
+        <v>3</v>
       </c>
     </row>
   </sheetData>
@@ -966,7 +2222,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F1"/>
+  <dimension ref="A1:F4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1001,6 +2257,78 @@
         </is>
       </c>
     </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>CKN12304-ND</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>PTS636 SP43 LFS</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>TACT 6.0 X 3.5, 4.3 MM H, 320GF,</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr"/>
+      <c r="E2" t="n">
+        <v>0.133</v>
+      </c>
+      <c r="F2" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>CKN12222-1-ND</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>PTS526 SMG15 SMTR2 LFS</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>TACT 5.2 X 5.2, 1.5 MM H, 160GF,</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr"/>
+      <c r="E3" t="n">
+        <v>0.207</v>
+      </c>
+      <c r="F3" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>CKN12317-1-ND</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>PTS636 SM43J SMTR LFS</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>TACT 6.0 X 3.5, 4.3 MM H, 180GF,</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr"/>
+      <c r="E4" t="n">
+        <v>0.211</v>
+      </c>
+      <c r="F4" t="n">
+        <v>10</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Saved_Lists/Inventory.xlsx
+++ b/Saved_Lists/Inventory.xlsx
@@ -636,7 +636,7 @@
         <v>5.86</v>
       </c>
       <c r="F8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="9">
@@ -802,7 +802,7 @@
         <v>0.77</v>
       </c>
       <c r="F5" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
     </row>
     <row r="6">
@@ -826,7 +826,7 @@
         <v>0.29</v>
       </c>
       <c r="F6" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
     </row>
     <row r="7">
@@ -850,7 +850,7 @@
         <v>0.46</v>
       </c>
       <c r="F7" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
     </row>
   </sheetData>
@@ -1086,7 +1086,7 @@
         <v>21.84</v>
       </c>
       <c r="F6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="7">
@@ -1110,7 +1110,7 @@
         <v>28.74</v>
       </c>
       <c r="F7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="8">
@@ -1134,7 +1134,7 @@
         <v>14.13</v>
       </c>
       <c r="F8" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="9">
@@ -1158,7 +1158,7 @@
         <v>2.45</v>
       </c>
       <c r="F9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="10">
@@ -1706,201 +1706,201 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
+          <t>Part Number</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Manufacturer Part Number</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Description</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Customer Reference</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Unit Price</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
           <t>Quantity</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>Part Number</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>Manufacturer Part Number</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>Description</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>Customer Reference</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>Unit Price</t>
-        </is>
-      </c>
     </row>
     <row r="2">
-      <c r="A2" t="n">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>788-1091-ND</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>4006-020</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>IC CURRENT REGULATOR MODULE</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr"/>
+      <c r="E2" t="n">
+        <v>3.97</v>
+      </c>
+      <c r="F2" t="n">
         <v>2</v>
       </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>788-1091-ND</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>4006-020</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>IC CURRENT REGULATOR MODULE</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr"/>
-      <c r="F2" t="n">
-        <v>3.97</v>
-      </c>
     </row>
     <row r="3">
-      <c r="A3" t="n">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>296-1414-5-ND</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>RC4558P</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>IC OPAMP GP 2 CIRCUIT 8DIP</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr"/>
+      <c r="E3" t="n">
+        <v>0.63</v>
+      </c>
+      <c r="F3" t="n">
         <v>5</v>
       </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>296-1414-5-ND</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>RC4558P</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>IC OPAMP GP 2 CIRCUIT 8DIP</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr"/>
-      <c r="F3" t="n">
-        <v>0.63</v>
-      </c>
     </row>
     <row r="4">
-      <c r="A4" t="n">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>296-NE555P-ND</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>NE555P</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>IC OSC SINGLE TIMER 100KHZ 8-DIP</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr"/>
+      <c r="E4" t="n">
+        <v>0.59</v>
+      </c>
+      <c r="F4" t="n">
         <v>5</v>
       </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>296-NE555P-ND</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>NE555P</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>IC OSC SINGLE TIMER 100KHZ 8-DIP</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr"/>
-      <c r="F4" t="n">
-        <v>0.59</v>
-      </c>
     </row>
     <row r="5">
-      <c r="A5" t="n">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>296-43515-5-ND</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>LM2679S-ADJ/NOPB</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>IC REG BUCK ADJ 5A TO263-7</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr"/>
+      <c r="E5" t="n">
+        <v>11.01</v>
+      </c>
+      <c r="F5" t="n">
         <v>3</v>
       </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>296-43515-5-ND</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>LM2679S-ADJ/NOPB</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>IC REG BUCK ADJ 5A TO263-7</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr"/>
-      <c r="F5" t="n">
-        <v>11.01</v>
-      </c>
     </row>
     <row r="6">
-      <c r="A6" t="n">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>296-14118-5-ND</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>CD4056BE</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>IC DRVR 7 SEGMENT 1 DIGIT 16DIP</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr"/>
+      <c r="E6" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="F6" t="n">
         <v>3</v>
       </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>296-14118-5-ND</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>CD4056BE</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>IC DRVR 7 SEGMENT 1 DIGIT 16DIP</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr"/>
-      <c r="F6" t="n">
-        <v>1.02</v>
-      </c>
     </row>
     <row r="7">
-      <c r="A7" t="n">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>296-31512-1-ND</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>CD4056BM96</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>IC DRVR 7 SEGMENT 1 DIGIT 16SOIC</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr"/>
+      <c r="E7" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="F7" t="n">
         <v>3</v>
       </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>296-31512-1-ND</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>CD4056BM96</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>IC DRVR 7 SEGMENT 1 DIGIT 16SOIC</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr"/>
-      <c r="F7" t="n">
-        <v>0.8</v>
-      </c>
     </row>
     <row r="8">
-      <c r="A8" t="n">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>AS78L05RTR-G1DICT-ND</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>AS78L05RTR-G1</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>IC REG LINEAR 5V 100MA SOT89-3</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr"/>
+      <c r="E8" t="n">
+        <v>0.505</v>
+      </c>
+      <c r="F8" t="n">
         <v>10</v>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>AS78L05RTR-G1DICT-ND</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>AS78L05RTR-G1</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>IC REG LINEAR 5V 100MA SOT89-3</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr"/>
-      <c r="F8" t="n">
-        <v>0.505</v>
       </c>
     </row>
   </sheetData>
@@ -2042,7 +2042,7 @@
         <v>3.54</v>
       </c>
       <c r="F5" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="6">

--- a/Saved_Lists/Inventory.xlsx
+++ b/Saved_Lists/Inventory.xlsx
@@ -487,12 +487,20 @@
           <t>RES 9.76K OHM 1% 1/8W 0805</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr"/>
-      <c r="E2" t="n">
-        <v>0.062</v>
-      </c>
-      <c r="F2" t="n">
-        <v>20</v>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>9.76K Resistor</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>0.06</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
       </c>
     </row>
     <row r="3">

--- a/Saved_Lists/Inventory.xlsx
+++ b/Saved_Lists/Inventory.xlsx
@@ -492,15 +492,11 @@
           <t>9.76K Resistor</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>0.06</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
+      <c r="E2" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="F2" t="n">
+        <v>20</v>
       </c>
     </row>
     <row r="3">
@@ -519,12 +515,20 @@
           <t>RES SMD 4.99K OHM 1% 1/8W 0805</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr"/>
-      <c r="E3" t="n">
-        <v>0.092</v>
-      </c>
-      <c r="F3" t="n">
-        <v>20</v>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>0.09</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
       </c>
     </row>
     <row r="4">
@@ -639,7 +643,11 @@
           <t>RES CHAS MNT 5 OHM 1% 50W</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr"/>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Load Resistor</t>
+        </is>
+      </c>
       <c r="E8" t="n">
         <v>5.86</v>
       </c>

--- a/Saved_Lists/Inventory.xlsx
+++ b/Saved_Lists/Inventory.xlsx
@@ -515,11 +515,7 @@
           <t>RES SMD 4.99K OHM 1% 1/8W 0805</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
+      <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr">
         <is>
           <t>0.09</t>

--- a/Saved_Lists/Inventory.xlsx
+++ b/Saved_Lists/Inventory.xlsx
@@ -516,15 +516,11 @@
         </is>
       </c>
       <c r="D3" t="inlineStr"/>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>0.09</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
+      <c r="E3" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="F3" t="n">
+        <v>20</v>
       </c>
     </row>
     <row r="4">

--- a/Saved_Lists/Inventory.xlsx
+++ b/Saved_Lists/Inventory.xlsx
@@ -515,12 +515,20 @@
           <t>RES SMD 4.99K OHM 1% 1/8W 0805</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr"/>
-      <c r="E3" t="n">
-        <v>0.09</v>
-      </c>
-      <c r="F3" t="n">
-        <v>20</v>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>kk</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>0.09</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
       </c>
     </row>
     <row r="4">

--- a/Saved_Lists/Inventory.xlsx
+++ b/Saved_Lists/Inventory.xlsx
@@ -515,11 +515,7 @@
           <t>RES SMD 4.99K OHM 1% 1/8W 0805</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>kk</t>
-        </is>
-      </c>
+      <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr">
         <is>
           <t>0.09</t>

--- a/Saved_Lists/Inventory.xlsx
+++ b/Saved_Lists/Inventory.xlsx
@@ -487,10 +487,8 @@
           <t>RES 9.76K OHM 1% 1/8W 0805</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>9.76K Resistor</t>
-        </is>
+      <c r="D2" t="n">
+        <v>1</v>
       </c>
       <c r="E2" t="n">
         <v>0.06</v>
@@ -639,11 +637,7 @@
           <t>RES CHAS MNT 5 OHM 1% 50W</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>Load Resistor</t>
-        </is>
-      </c>
+      <c r="D8" t="inlineStr"/>
       <c r="E8" t="n">
         <v>5.86</v>
       </c>

--- a/Saved_Lists/Inventory.xlsx
+++ b/Saved_Lists/Inventory.xlsx
@@ -487,14 +487,16 @@
           <t>RES 9.76K OHM 1% 1/8W 0805</t>
         </is>
       </c>
-      <c r="D2" t="n">
-        <v>1</v>
-      </c>
-      <c r="E2" t="n">
-        <v>0.06</v>
-      </c>
-      <c r="F2" t="n">
-        <v>20</v>
+      <c r="D2" t="inlineStr"/>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>0.06</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
       </c>
     </row>
     <row r="3">
@@ -514,15 +516,11 @@
         </is>
       </c>
       <c r="D3" t="inlineStr"/>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>0.09</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
+      <c r="E3" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="F3" t="n">
+        <v>20</v>
       </c>
     </row>
     <row r="4">
@@ -614,8 +612,10 @@
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
-      <c r="E7" t="n">
-        <v>0.0253</v>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>0.03</t>
+        </is>
       </c>
       <c r="F7" t="n">
         <v>100</v>

--- a/Saved_Lists/Inventory.xlsx
+++ b/Saved_Lists/Inventory.xlsx
@@ -485,7 +485,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>RES 9.76K OHM 1% 1/8W 0805</t>
+          <t>Resistor 9.76K OHM 1% 1/8W 0805</t>
         </is>
       </c>
       <c r="D2" t="inlineStr"/>
@@ -509,7 +509,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>RES SMD 4.99K OHM 1% 1/8W 0805</t>
+          <t>Resistor SMD 4.99K OHM 1% 1/8W 0805</t>
         </is>
       </c>
       <c r="D3" t="inlineStr"/>
@@ -533,7 +533,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>RES 1 OHM 1% 1/8W 0805</t>
+          <t>Resistor 1 OHM 1% 1/8W 0805</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
@@ -557,7 +557,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>RES 1K OHM 1% 1/8W 0805</t>
+          <t>Resistor 1K OHM 1% 1/8W 0805</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
@@ -581,7 +581,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>RES 10K OHM 1% 1/4W 0805</t>
+          <t>Resistor 10K OHM 1% 1/4W 0805</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
@@ -605,7 +605,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>RES 220 OHM 1% 1/4W 0805</t>
+          <t>Resistor 220 OHM 1% 1/4W 0805</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
@@ -629,7 +629,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>RES CHAS MNT 5 OHM 1% 50W</t>
+          <t>Resistor CHAS MNT 5 OHM 1% 50W</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
@@ -653,7 +653,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>RES 1.47K OHM 1% 1/8W 0805</t>
+          <t>Resistor 1.47K OHM 1% 1/8W 0805</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
@@ -1291,7 +1291,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>CAP CER 10000PF 100V X7R 0805</t>
+          <t>Capacitor CER 10000PF 100V X7R 0805</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -1319,7 +1319,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>CAP CER 0.1UF 50V X7R 0805</t>
+          <t>Capacitor CER 0.1UF 50V X7R 0805</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -1347,7 +1347,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>CAP ALUM POLY 22UF 20% 35V SMD</t>
+          <t>Capacitor ALUM POLY 22UF 20% 35V SMD</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
@@ -1371,7 +1371,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>CAP ALUM POLY 100UF 20% 50V SMD</t>
+          <t>Capacitor ALUM POLY 100UF 20% 50V SMD</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
@@ -1395,7 +1395,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>CAP CER 0.1UF 10V X7R 0402</t>
+          <t>Capacitor CER 0.1UF 10V X7R 0402</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
@@ -1465,7 +1465,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>FIXED IND 33UH 5A 75.4 MOHM SMD</t>
+          <t>FIXED Inductor 33UH 5A 75.4 MOHM SMD</t>
         </is>
       </c>
       <c r="D2" t="inlineStr"/>
